--- a/AAII_Financials/Quarterly/PHG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PHG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="92">
   <si>
     <t>PHG</t>
   </si>
@@ -656,542 +656,555 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4981100</v>
+      </c>
+      <c r="E8" s="3">
         <v>4502500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5985700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5047500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5094500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4428200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5222100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4881800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5595200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4879900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5595200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4732200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4879900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4527400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6005400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4657800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4545000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4251000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5359800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4475600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4475300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3906600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5221400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4578200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4335300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4169800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6955400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5759900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5495000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4965400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6607700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4769300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>9035400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>4328300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>10603900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>4654000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>9345100</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>4736300</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>6228200</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>4879500</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2524800</v>
+      </c>
+      <c r="E9" s="3">
         <v>2467400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3299300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2806500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2732800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2429700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3189800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2644400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3606700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2738000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3606700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2686300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2738000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2619500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3545400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2788200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2660400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2611600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3279400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2349800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2582600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2388700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2703000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2519000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2525500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2305600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3795200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3120000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2995100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2707000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3428000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2472200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>4872900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2367300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>5579700</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>2504300</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>5191400</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>2650500</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>3316000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>2587100</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2456300</v>
+      </c>
+      <c r="E10" s="3">
         <v>2035100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2686400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2241000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2361700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1998500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2032300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2237300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1988500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2141900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1988500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2045900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2141900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1907900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2460000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1869600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1884600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1639400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2080400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2125800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1892800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1517900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2518400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2059200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1809800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1864100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3160200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2639900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2499900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2258400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3179600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2297200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>4162500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1961000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>5024300</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>2149700</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>4153600</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>2085900</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>2912200</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>2292500</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1234,130 +1247,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>553000</v>
+      </c>
+      <c r="E12" s="3">
         <v>454300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>501400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>485700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>472100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>493900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>488700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>482900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>496300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>510900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>496300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>471000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>510900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>573700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>557100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>664600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>533200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>537100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>514900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>470600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>497300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>432800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>463800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>473300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>473500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>526200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>636200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>559800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>521100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>525100</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>574900</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>459700</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>942100</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>475400</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>1023300</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>506000</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>955900</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>505900</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>527000</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>502400</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1478,59 +1495,62 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="3">
         <v>58700</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" s="3">
         <v>-1000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>640000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N14" s="3">
         <v>640000</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R14" s="3">
         <v>28800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1438400</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1546,12 +1566,12 @@
       <c r="X14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z14" s="3">
         <v>143600</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1570,83 +1590,86 @@
       <c r="AF14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH14" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>-48300</v>
       </c>
-      <c r="AJ14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK14" s="3">
-        <v>0</v>
+      <c r="AK14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AL14" s="3">
         <v>0</v>
       </c>
       <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3">
         <v>10100</v>
       </c>
-      <c r="AN14" s="3">
-        <v>0</v>
-      </c>
       <c r="AO14" s="3">
         <v>0</v>
       </c>
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>435300</v>
+      </c>
+      <c r="E15" s="3">
         <v>305500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>327600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>355500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>312400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>298300</v>
       </c>
-      <c r="I15" s="3">
-        <v>169500</v>
-      </c>
       <c r="J15" s="3">
+        <v>477300</v>
+      </c>
+      <c r="K15" s="3">
         <v>324600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>196200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>335700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>196200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>199500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>335700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>204800</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1722,8 +1745,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1763,252 +1789,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4284200</v>
+      </c>
+      <c r="E17" s="3">
         <v>4224600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5343400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4661500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4623600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4260700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5054400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4501400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4980700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4637600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4980700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4496200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4637600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5160800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5816000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6310200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4533000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4447400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5184200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4090100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4385400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3959700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4569100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4167200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4111600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4158500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6104400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5367900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5083200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4672400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5698000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4269800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>8487500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4107600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>9508900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>4337600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>8908600</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>4537900</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>5423000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>4440500</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>696900</v>
+      </c>
+      <c r="E18" s="3">
         <v>277900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>642200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>386000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>470900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>167500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>167700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>380300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>614600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>242400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>614600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>236000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>242400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-633400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>189400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1652400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>12000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-196400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>175600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>385500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>89900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-53100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>652300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>411000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>223600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>11300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>851000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>392000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>411700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>293100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>909700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>499500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>547900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>220700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1095100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>316400</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>436500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>198400</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>805200</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>439000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2051,297 +2084,304 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E20" s="3">
         <v>3500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>9400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>7000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>70400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>24500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>94000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>41500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>61900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>19100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>41500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>16300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-181600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>47600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-49000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-41200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-31400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-8600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-9500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-19900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-32200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>22900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-26000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-66500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-42900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-18800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-9600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-68600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-33200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-140500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-86700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>5600</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-15700</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>7900</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>25800</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-70400</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-206600</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1129900</v>
+      </c>
+      <c r="E21" s="3">
         <v>580000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>960400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>745000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>776300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>464800</v>
       </c>
-      <c r="I21" s="3">
-        <v>266800</v>
-      </c>
       <c r="J21" s="3">
+        <v>574600</v>
+      </c>
+      <c r="K21" s="3">
         <v>680300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>716800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>536600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>748900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>416500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>536600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-444900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1200600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1789600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>334000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>147600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1243500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-12900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>497300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>231700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1752400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-48800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>664400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>400800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2034800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>18400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>767000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>622000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1840600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>130700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1008000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>387600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1721100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>81900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>973900</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>329800</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>806400</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>757100</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>108500</v>
+      </c>
+      <c r="E22" s="3">
         <v>95700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>38700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>91500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>94000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>88600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>-12400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>116000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>-13300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>91700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>18800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>96300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>91700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>101000</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -2417,252 +2457,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>623800</v>
+      </c>
+      <c r="E23" s="3">
         <v>219100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>548300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>322700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>396900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>113500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>119100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>274400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-103900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>126600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-103900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>136500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>126600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-735500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>7800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1604800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-37000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-237600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>144200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>376900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>80400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-51000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>632400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>378800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>246500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-14700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>784500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>349100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>392900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>283500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>841000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>466300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>407400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>134000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1100700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>300700</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>444300</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>224200</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>734800</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>232400</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>182800</v>
+      </c>
+      <c r="E24" s="3">
         <v>50700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>86900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>102100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>111600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>29200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>464900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>72500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-145900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>45900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-145900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>33900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>45900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-16300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>132900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-168600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-10900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-72700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-6500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-99100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>11600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-16300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>125700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>89300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>32700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-33900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>142400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>91900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>87100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>78900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-14200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>126300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>99900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>30700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>271500</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>5600</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>120100</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>74000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>187800</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>-18800</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2783,252 +2832,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>441000</v>
+      </c>
+      <c r="E26" s="3">
         <v>168300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>461400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>220600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>285400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>84300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-345800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>201900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>42000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>80800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>42000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>102700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>80800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-719300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-125200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1436300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-26100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-164900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>150700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>476000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>68800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-34700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>506700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>289600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>213800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>19200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>642100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>257200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>305900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>204600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>855200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>340000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>307400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>103200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>829200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>295100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>324300</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>150200</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>547000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>251200</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>438700</v>
+      </c>
+      <c r="E27" s="3">
         <v>174100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>463800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>215900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>281900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>82100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-346800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>201900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>43100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>78600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>43100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>93100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>78600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-722500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-125200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1438400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-28300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-163800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>157200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>468500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>65600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-33700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>501700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>288500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>211600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>18100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>639700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>254800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>300000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>206900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>848100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>338900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>307400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>104300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>663100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>173900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>250200</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>117400</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>530600</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>244200</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3149,8 +3207,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3158,121 +3219,124 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>4700</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-1200</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-2300</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-6500</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-1100</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-1100</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-7400</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>8900</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>1100</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>4400</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>13000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>2733200</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>93100</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>74500</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>98700</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>63300</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>15300</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>24800</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>7000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-15300</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-10800</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-52000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-16600</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-169100</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>32900</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>655200</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>179500</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3">
         <v>290600</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>153800</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AP29" s="3">
         <v>204200</v>
       </c>
-      <c r="AP29" s="3">
+      <c r="AQ29" s="3">
         <v>198400</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3393,8 +3457,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3515,252 +3582,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-9400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-7000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-70400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-24500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-94000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-41500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-61900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-19100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-41500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-16300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>181600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-47600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>49000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>41200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>31400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>8600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>9500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>19900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>32200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-22900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>26000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>66500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>42900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>18800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>9600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>68600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>33200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>140500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>86700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-5600</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>15700</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-7900</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-25800</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>70400</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>206600</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>438700</v>
+      </c>
+      <c r="E33" s="3">
         <v>174100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>463800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>215900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>281900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>82100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-346800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>201900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>43100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>78600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>43100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>93100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>78600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-722500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-116300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1437300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-23900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-163800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>170200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3201600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>158700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>40800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>600400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>351800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>226900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>42900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>646700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>251100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>284700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>196200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>796100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>322300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>138300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>137300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1318300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>353400</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>540800</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>271200</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>734800</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>442500</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3881,257 +3957,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>438700</v>
+      </c>
+      <c r="E35" s="3">
         <v>174100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>463800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>215900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>281900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>82100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-346800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>201900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>43100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>78600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>43100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>93100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>78600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-722500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-116300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1437300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-23900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-163800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>170200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3201600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>158700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>40800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>600400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>351800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>226900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>42900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>646700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>251100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>284700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>196200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>796100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>322300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>138300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>137300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1318300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>353400</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>540800</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>271200</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>734800</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>442500</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4174,8 +4259,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4218,130 +4304,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2043900</v>
+      </c>
+      <c r="E41" s="3">
         <v>2988600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3280500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2243300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2139800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1289500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2485800</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L41" s="3">
         <v>2065900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1048000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2065900</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O41" s="3">
+      <c r="O41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P41" s="3">
         <v>1048000</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q41" s="3">
+      <c r="Q41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R41" s="3">
         <v>1298100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>838600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1368800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1567800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2496700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4121300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1061200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1061600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3217600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2584400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2502500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2419700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1663600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1351200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1267000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1739300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1996700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1391100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1773300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2176200</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2175500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1120900</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>2490800</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>3205700</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>2739700</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>2182100</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4355,969 +4445,993 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>2300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2200</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>3300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>8700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>3300</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>8700</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>12200</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="S42" s="3">
+      <c r="S42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T42" s="3">
         <v>8700</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="U42" s="3">
+      <c r="U42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V42" s="3">
         <v>2200</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W42" s="3" t="s">
         <v>10</v>
       </c>
       <c r="X42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC42" s="3">
+      <c r="Y42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD42" s="3">
         <v>1200</v>
       </c>
-      <c r="AD42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE42" s="3">
+      <c r="AE42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF42" s="3">
         <v>560000</v>
       </c>
-      <c r="AF42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG42" s="3">
+      <c r="AG42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH42" s="3">
         <v>515700</v>
       </c>
-      <c r="AH42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI42" s="3">
+      <c r="AI42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ42" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK42" s="3">
-        <v>2200</v>
+      <c r="AK42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AL42" s="3">
         <v>2200</v>
       </c>
       <c r="AM42" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="AN42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="3">
         <v>113900</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>118600</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>120900</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4109400</v>
+      </c>
+      <c r="E43" s="3">
         <v>3813000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4624900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3896500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3907200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3758100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4261300</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L43" s="3">
         <v>4697700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4220500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4697700</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O43" s="3">
+      <c r="O43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P43" s="3">
         <v>4220500</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q43" s="3">
+      <c r="Q43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R43" s="3">
         <v>4803700</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="S43" s="3">
+      <c r="S43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T43" s="3">
         <v>4147800</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="U43" s="3">
+      <c r="U43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V43" s="3">
         <v>4300600</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="W43" s="3">
+      <c r="W43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X43" s="3">
         <v>3713600</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y43" s="3">
+      <c r="Y43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z43" s="3">
         <v>4294800</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA43" s="3">
+      <c r="AA43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB43" s="3">
         <v>4165100</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC43" s="3">
+      <c r="AC43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD43" s="3">
         <v>5523000</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE43" s="3">
+      <c r="AE43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF43" s="3">
         <v>4666800</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG43" s="3">
+      <c r="AG43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH43" s="3">
         <v>4946900</v>
       </c>
-      <c r="AH43" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI43" s="3">
+      <c r="AI43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ43" s="3">
         <v>3952800</v>
       </c>
-      <c r="AJ43" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK43" s="3">
+      <c r="AK43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL43" s="3">
         <v>4508200</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>3888800</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>3707100</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>5654200</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>6433700</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>5792800</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3674200</v>
+      </c>
+      <c r="E44" s="3">
         <v>3585800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3369700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3824900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3795700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3600300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3310900</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L44" s="3">
         <v>3858700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4470500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3858700</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O44" s="3">
+      <c r="O44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P44" s="3">
         <v>4470500</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q44" s="3">
+      <c r="Q44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R44" s="3">
         <v>4484700</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="S44" s="3">
+      <c r="S44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T44" s="3">
         <v>4461200</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="U44" s="3">
+      <c r="U44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V44" s="3">
         <v>3740100</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="W44" s="3">
+      <c r="W44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X44" s="3">
         <v>3412100</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y44" s="3">
+      <c r="Y44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z44" s="3">
         <v>2985200</v>
       </c>
-      <c r="Z44" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA44" s="3">
+      <c r="AA44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB44" s="3">
         <v>3483300</v>
       </c>
-      <c r="AB44" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC44" s="3">
+      <c r="AC44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD44" s="3">
         <v>3237200</v>
       </c>
-      <c r="AD44" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE44" s="3">
+      <c r="AE44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF44" s="3">
         <v>3508000</v>
       </c>
-      <c r="AF44" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG44" s="3">
+      <c r="AG44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH44" s="3">
         <v>3163100</v>
       </c>
-      <c r="AH44" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI44" s="3">
+      <c r="AI44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ44" s="3">
         <v>2964600</v>
       </c>
-      <c r="AJ44" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK44" s="3">
+      <c r="AK44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL44" s="3">
         <v>2640000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>3019300</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>2876800</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>4259800</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>3981600</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>4412400</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>831700</v>
+      </c>
+      <c r="E45" s="3">
         <v>893600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>174900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>921000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>798600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>719800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>71400</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L45" s="3">
         <v>143700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>826400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>143700</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P45" s="3">
         <v>826400</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R45" s="3">
         <v>764200</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="S45" s="3">
+      <c r="S45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T45" s="3">
         <v>934700</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="U45" s="3">
+      <c r="U45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V45" s="3">
         <v>677600</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="W45" s="3">
+      <c r="W45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X45" s="3">
         <v>1790100</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y45" s="3">
+      <c r="Y45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z45" s="3">
         <v>700200</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA45" s="3">
+      <c r="AA45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB45" s="3">
         <v>732000</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC45" s="3">
+      <c r="AC45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD45" s="3">
         <v>617600</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE45" s="3">
+      <c r="AE45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF45" s="3">
         <v>676400</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG45" s="3">
+      <c r="AG45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH45" s="3">
         <v>700300</v>
       </c>
-      <c r="AH45" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI45" s="3">
+      <c r="AI45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ45" s="3">
         <v>1260500</v>
       </c>
-      <c r="AJ45" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK45" s="3">
+      <c r="AK45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL45" s="3">
         <v>2025200</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>8397000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>8313900</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>3091800</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>3247900</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>3048400</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10659200</v>
+      </c>
+      <c r="E46" s="3">
         <v>11281000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>11661400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10885800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10643600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9369900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10375800</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L46" s="3">
         <v>10987100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10574200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10987100</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O46" s="3">
+      <c r="O46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P46" s="3">
         <v>10574200</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q46" s="3">
+      <c r="Q46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R46" s="3">
         <v>11362900</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="S46" s="3">
+      <c r="S46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T46" s="3">
         <v>10921300</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="U46" s="3">
+      <c r="U46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V46" s="3">
         <v>11217200</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="W46" s="3">
+      <c r="W46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X46" s="3">
         <v>9976900</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y46" s="3">
+      <c r="Y46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z46" s="3">
         <v>11197800</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA46" s="3">
+      <c r="AA46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB46" s="3">
         <v>10882900</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC46" s="3">
+      <c r="AC46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD46" s="3">
         <v>11042500</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE46" s="3">
+      <c r="AE46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF46" s="3">
         <v>10678200</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG46" s="3">
+      <c r="AG46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH46" s="3">
         <v>11322700</v>
       </c>
-      <c r="AH46" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI46" s="3">
+      <c r="AI46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ46" s="3">
         <v>9952300</v>
       </c>
-      <c r="AJ46" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK46" s="3">
+      <c r="AK46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL46" s="3">
         <v>11351200</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>16428200</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>17388600</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>16325300</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>16521400</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>15556500</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>984800</v>
+      </c>
+      <c r="E47" s="3">
         <v>980100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1000400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>897600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>916000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>915500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>919300</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L47" s="3">
         <v>1105300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1203100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1105300</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P47" s="3">
         <v>1203100</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R47" s="3">
         <v>1634800</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="S47" s="3">
+      <c r="S47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T47" s="3">
         <v>1686600</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="U47" s="3">
+      <c r="U47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V47" s="3">
         <v>1387600</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="W47" s="3">
+      <c r="W47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X47" s="3">
         <v>1215600</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y47" s="3">
+      <c r="Y47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z47" s="3">
         <v>897700</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA47" s="3">
+      <c r="AA47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB47" s="3">
         <v>860700</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC47" s="3">
+      <c r="AC47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD47" s="3">
         <v>769300</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE47" s="3">
+      <c r="AE47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF47" s="3">
         <v>903500</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG47" s="3">
+      <c r="AG47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH47" s="3">
         <v>906100</v>
       </c>
-      <c r="AH47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI47" s="3">
+      <c r="AI47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ47" s="3">
         <v>1079300</v>
       </c>
-      <c r="AJ47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK47" s="3">
+      <c r="AK47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL47" s="3">
         <v>963800</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1005300</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>1067000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>855700</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>798200</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>849800</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2479200</v>
+      </c>
+      <c r="E48" s="3">
         <v>2514700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2603000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2603500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2654100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2582100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2538600</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L48" s="3">
         <v>2744600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2750000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2744600</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O48" s="3">
+      <c r="O48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P48" s="3">
         <v>2750000</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q48" s="3">
+      <c r="Q48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R48" s="3">
         <v>2921800</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="S48" s="3">
+      <c r="S48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T48" s="3">
         <v>2984700</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="U48" s="3">
+      <c r="U48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V48" s="3">
         <v>2926000</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="W48" s="3">
+      <c r="W48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X48" s="3">
         <v>2871400</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y48" s="3">
+      <c r="Y48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z48" s="3">
         <v>2675000</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA48" s="3">
+      <c r="AA48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB48" s="3">
         <v>3080700</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC48" s="3">
+      <c r="AC48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD48" s="3">
         <v>3345800</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE48" s="3">
+      <c r="AE48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF48" s="3">
         <v>2909200</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG48" s="3">
+      <c r="AG48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH48" s="3">
         <v>2025100</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI48" s="3">
+      <c r="AI48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>1731500</v>
       </c>
-      <c r="AJ48" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK48" s="3">
+      <c r="AK48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL48" s="3">
         <v>1785100</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1742500</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1705400</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>2490800</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>2529600</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>2577700</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>13987200</v>
+      </c>
+      <c r="E49" s="3">
         <v>14177300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>13313400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>13985700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14180900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14026200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>13404100</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
         <v>14071000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14588400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>14071000</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
       <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
         <v>14588400</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
-      </c>
       <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3">
         <v>15245000</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="S49" s="3">
+      <c r="S49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T49" s="3">
         <v>16905800</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="U49" s="3">
+      <c r="U49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V49" s="3">
         <v>15488500</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="W49" s="3">
+      <c r="W49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X49" s="3">
         <v>14620500</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y49" s="3">
+      <c r="Y49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z49" s="3">
         <v>10982400</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA49" s="3">
+      <c r="AA49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB49" s="3">
         <v>12958900</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC49" s="3">
+      <c r="AC49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD49" s="3">
         <v>14149000</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE49" s="3">
+      <c r="AE49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF49" s="3">
         <v>14293300</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG49" s="3">
+      <c r="AG49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH49" s="3">
         <v>14303600</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI49" s="3">
+      <c r="AI49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ49" s="3">
         <v>12557800</v>
       </c>
-      <c r="AJ49" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK49" s="3">
+      <c r="AK49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL49" s="3">
         <v>12401400</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>12657200</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>10311100</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>14311100</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>25058500</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>14000000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5438,8 +5552,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5560,130 +5677,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>377000</v>
+      </c>
+      <c r="E52" s="3">
         <v>393200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>387500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>421200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>473300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>398800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>344800</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L52" s="3">
         <v>320500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>393000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>320500</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P52" s="3">
         <v>393000</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q52" s="3">
+      <c r="Q52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R52" s="3">
         <v>2825500</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="S52" s="3">
+      <c r="S52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T52" s="3">
         <v>2854100</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="U52" s="3">
+      <c r="U52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V52" s="3">
         <v>2545500</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="W52" s="3">
+      <c r="W52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X52" s="3">
         <v>2003900</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y52" s="3">
+      <c r="Y52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z52" s="3">
         <v>1888100</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA52" s="3">
+      <c r="AA52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB52" s="3">
         <v>2198200</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC52" s="3">
+      <c r="AC52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD52" s="3">
         <v>2232100</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE52" s="3">
+      <c r="AE52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF52" s="3">
         <v>2216300</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG52" s="3">
+      <c r="AG52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH52" s="3">
         <v>2220300</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI52" s="3">
+      <c r="AI52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>1935800</v>
       </c>
-      <c r="AJ52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK52" s="3">
+      <c r="AK52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL52" s="3">
         <v>1901800</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>2585100</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>2546900</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>3419300</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>3415800</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>3298400</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5804,130 +5927,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>30505000</v>
+      </c>
+      <c r="E54" s="3">
         <v>31437800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>31635600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>30903400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>30979400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>29363400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>29999000</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L54" s="3">
         <v>32503600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>32211800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>32503600</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O54" s="3">
+      <c r="O54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P54" s="3">
         <v>32211800</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q54" s="3">
+      <c r="Q54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R54" s="3">
         <v>33990000</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="S54" s="3">
+      <c r="S54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T54" s="3">
         <v>35352400</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="U54" s="3">
+      <c r="U54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V54" s="3">
         <v>33564800</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="W54" s="3">
+      <c r="W54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X54" s="3">
         <v>30688300</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y54" s="3">
+      <c r="Y54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z54" s="3">
         <v>27640900</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA54" s="3">
+      <c r="AA54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB54" s="3">
         <v>29981500</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC54" s="3">
+      <c r="AC54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD54" s="3">
         <v>31538700</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE54" s="3">
+      <c r="AE54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF54" s="3">
         <v>31000500</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG54" s="3">
+      <c r="AG54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH54" s="3">
         <v>30777900</v>
       </c>
-      <c r="AH54" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI54" s="3">
+      <c r="AI54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ54" s="3">
         <v>27256800</v>
       </c>
-      <c r="AJ54" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK54" s="3">
+      <c r="AK54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL54" s="3">
         <v>28403200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>34418200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>33019000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>37402300</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>37878800</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>36282500</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5970,8 +6099,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6014,740 +6144,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2376300</v>
+      </c>
+      <c r="E57" s="3">
         <v>2294500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2262500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2009900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2057500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1978000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1894600</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L57" s="3">
         <v>2118900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1796900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2118900</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P57" s="3">
         <v>1796900</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q57" s="3">
+      <c r="Q57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R57" s="3">
         <v>2179800</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="S57" s="3">
+      <c r="S57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T57" s="3">
         <v>1965100</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="U57" s="3">
+      <c r="U57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V57" s="3">
         <v>2029400</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="W57" s="3">
+      <c r="W57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X57" s="3">
         <v>1682200</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y57" s="3">
+      <c r="Y57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z57" s="3">
         <v>2113500</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA57" s="3">
+      <c r="AA57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB57" s="3">
         <v>2143600</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC57" s="3">
+      <c r="AC57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD57" s="3">
         <v>2438700</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE57" s="3">
+      <c r="AE57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF57" s="3">
         <v>2461000</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG57" s="3">
+      <c r="AG57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH57" s="3">
         <v>2724200</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI57" s="3">
+      <c r="AI57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ57" s="3">
         <v>1955500</v>
       </c>
-      <c r="AJ57" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK57" s="3">
+      <c r="AK57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL57" s="3">
         <v>2345000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1928700</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1919700</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>3404000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>3343000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>3081300</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1312700</v>
+      </c>
+      <c r="E58" s="3">
         <v>1390500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1351400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1346900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1461000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>554500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>544600</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>722900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1134300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>722900</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>1134300</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>1031200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1509700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1319900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>576100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>548600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1088700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2062000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1778200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1225800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>698500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>644700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>579200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>593000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1141700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1211700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1952200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1649000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1917300</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1360400</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1575600</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>754000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>346700</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>333200</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1614000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>1860500</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>1065800</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3141800</v>
+      </c>
+      <c r="E59" s="3">
         <v>3355200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2965800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3201900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3268300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3352800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3992100</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L59" s="3">
         <v>3858700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4179000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3858700</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P59" s="3">
         <v>4179000</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R59" s="3">
         <v>5576800</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="S59" s="3">
+      <c r="S59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T59" s="3">
         <v>5887700</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="U59" s="3">
+      <c r="U59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V59" s="3">
         <v>5498600</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="W59" s="3">
+      <c r="W59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X59" s="3">
         <v>5535500</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y59" s="3">
+      <c r="Y59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z59" s="3">
         <v>4375600</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA59" s="3">
+      <c r="AA59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB59" s="3">
         <v>5383600</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC59" s="3">
+      <c r="AC59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD59" s="3">
         <v>5114400</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE59" s="3">
+      <c r="AE59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF59" s="3">
         <v>4713800</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG59" s="3">
+      <c r="AG59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH59" s="3">
         <v>5022600</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI59" s="3">
+      <c r="AI59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>4505100</v>
       </c>
-      <c r="AJ59" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK59" s="3">
+      <c r="AK59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL59" s="3">
         <v>4604600</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>9424700</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>9397800</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>6487600</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>7089800</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>6617900</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8479400</v>
+      </c>
+      <c r="E60" s="3">
         <v>8568000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8816500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8248300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8456800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7302200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8433600</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L60" s="3">
         <v>9159900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8811100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9159900</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O60" s="3">
+      <c r="O60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P60" s="3">
         <v>8811100</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q60" s="3">
+      <c r="Q60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R60" s="3">
         <v>8787700</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="S60" s="3">
+      <c r="S60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T60" s="3">
         <v>9172700</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="U60" s="3">
+      <c r="U60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V60" s="3">
         <v>8076500</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="W60" s="3">
+      <c r="W60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X60" s="3">
         <v>9279700</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y60" s="3">
+      <c r="Y60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z60" s="3">
         <v>7714900</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA60" s="3">
+      <c r="AA60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB60" s="3">
         <v>8172000</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC60" s="3">
+      <c r="AC60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD60" s="3">
         <v>8146200</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE60" s="3">
+      <c r="AE60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF60" s="3">
         <v>8386600</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG60" s="3">
+      <c r="AG60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH60" s="3">
         <v>9395800</v>
       </c>
-      <c r="AH60" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI60" s="3">
+      <c r="AI60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ60" s="3">
         <v>7821100</v>
       </c>
-      <c r="AJ60" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK60" s="3">
+      <c r="AK60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL60" s="3">
         <v>7703600</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>11700100</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>11650700</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>11505700</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>12293300</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>10765000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7215800</v>
+      </c>
+      <c r="E61" s="3">
         <v>7945300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8141400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8491100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8434500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7626500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7364100</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>7776100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7835200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7776100</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>7835200</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>8052300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7467600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>7386000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>7026500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7017400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7132300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>6223200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5999200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5690200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6801400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>7314600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>7178800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5765800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5929000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5632600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>4839800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>4053800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3512200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>4049400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>3559700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>4537300</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>4982800</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>2916100</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>4658900</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>4719900</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>5704700</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1080800</v>
+      </c>
+      <c r="E62" s="3">
         <v>1149500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>517800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1169800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1291800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1227800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>623300</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L62" s="3">
         <v>1022400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1677900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1022400</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P62" s="3">
         <v>1677900</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q62" s="3">
+      <c r="Q62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R62" s="3">
         <v>2437800</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="S62" s="3">
+      <c r="S62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T62" s="3">
         <v>2726800</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="U62" s="3">
+      <c r="U62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V62" s="3">
         <v>2778500</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="W62" s="3">
+      <c r="W62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X62" s="3">
         <v>2503200</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y62" s="3">
+      <c r="Y62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z62" s="3">
         <v>2365800</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA62" s="3">
+      <c r="AA62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB62" s="3">
         <v>2515600</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC62" s="3">
+      <c r="AC62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD62" s="3">
         <v>2888200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>5719500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2944500</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG62" s="3">
+      <c r="AG62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH62" s="3">
         <v>2995100</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI62" s="3">
+      <c r="AI62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ62" s="3">
         <v>2538600</v>
       </c>
-      <c r="AJ62" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK62" s="3">
+      <c r="AK62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL62" s="3">
         <v>2672600</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>3183100</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>3028300</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>4769200</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>5074400</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>5171800</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6868,8 +7017,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6990,8 +7142,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7112,130 +7267,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>17394000</v>
+      </c>
+      <c r="E66" s="3">
         <v>18272800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>18733100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>18486400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>18756300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>16687200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>17530800</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L66" s="3">
         <v>19172100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>18936700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>19172100</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O66" s="3">
+      <c r="O66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P66" s="3">
         <v>18936700</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q66" s="3">
+      <c r="Q66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R66" s="3">
         <v>19315400</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="S66" s="3">
+      <c r="S66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T66" s="3">
         <v>19327900</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="U66" s="3">
+      <c r="U66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V66" s="3">
         <v>17911500</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="W66" s="3">
+      <c r="W66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X66" s="3">
         <v>18042100</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y66" s="3">
+      <c r="Y66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z66" s="3">
         <v>15801800</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA66" s="3">
+      <c r="AA66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB66" s="3">
         <v>18033800</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC66" s="3">
+      <c r="AC66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD66" s="3">
         <v>16832900</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE66" s="3">
+      <c r="AE66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF66" s="3">
         <v>16996600</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG66" s="3">
+      <c r="AG66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH66" s="3">
         <v>16479000</v>
       </c>
-      <c r="AH66" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI66" s="3">
+      <c r="AI66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ66" s="3">
         <v>14433200</v>
       </c>
-      <c r="AJ66" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK66" s="3">
+      <c r="AK66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL66" s="3">
         <v>14940400</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>21614000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>19279200</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>22497200</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>23152200</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>22642800</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7278,8 +7439,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7400,8 +7562,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7522,8 +7687,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7644,8 +7812,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7766,130 +7937,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3636500</v>
+      </c>
+      <c r="E72" s="3">
         <v>4282300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4198700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3762800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3561900</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J72" s="3">
         <v>3779900</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L72" s="3">
         <v>5969900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5838400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5969900</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P72" s="3">
         <v>5838400</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R72" s="3">
         <v>7567100</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T72" s="3">
         <v>8758100</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V72" s="3">
         <v>10129800</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="W72" s="3">
+      <c r="W72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X72" s="3">
         <v>7695900</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z72" s="3">
         <v>7807600</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA72" s="3">
+      <c r="AA72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB72" s="3">
         <v>7323300</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC72" s="3">
+      <c r="AC72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD72" s="3">
         <v>9684800</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF72" s="3">
         <v>8834800</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG72" s="3">
+      <c r="AG72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH72" s="3">
         <v>9777900</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI72" s="3">
+      <c r="AI72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ72" s="3">
         <v>8778500</v>
       </c>
-      <c r="AJ72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK72" s="3">
+      <c r="AK72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL72" s="3">
         <v>9644600</v>
       </c>
-      <c r="AL72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM72" s="3">
+      <c r="AM72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN72" s="3">
         <v>9333800</v>
       </c>
-      <c r="AN72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AO72" s="3">
+      <c r="AO72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP72" s="3">
         <v>9599400</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>9531300</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8010,8 +8187,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8132,8 +8312,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8254,130 +8437,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13077800</v>
+      </c>
+      <c r="E76" s="3">
         <v>13135000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12864900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12380600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12189100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12642700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12429900</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L76" s="3">
         <v>13295000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13238000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13295000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>12834500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13238000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>14394800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>14674600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>15602100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>16024400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>15691300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>15653300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>15680700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>12646300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>12752900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>11839100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>12166300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>11947600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13684700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14705900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>15136000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>14003900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14747900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>14298900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>13047500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>12823500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>12721400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>13462800</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>12804100</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>13739900</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>14905000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>14726600</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>13639700</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8498,257 +8687,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>438700</v>
+      </c>
+      <c r="E81" s="3">
         <v>174100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>463800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>215900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>281900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>82100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-346800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>201900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>43100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>78600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>43100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>93100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>78600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-722500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-116300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1437300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-23900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-163800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>170200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3201600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>158700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>40800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>600400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>351800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>226900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>42900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>646700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>251100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>284700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>196200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>796100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>322300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>138300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>137300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1318300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>353400</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>540800</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>271200</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>734800</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>442500</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8791,26 +8989,27 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>250100</v>
+      </c>
+      <c r="E83" s="3">
         <v>236700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-73500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>250900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>303200</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="I83" s="3" t="s">
         <v>10</v>
       </c>
@@ -8835,8 +9034,8 @@
       <c r="P83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -8890,31 +9089,34 @@
         <v>0</v>
       </c>
       <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>600600</v>
       </c>
-      <c r="AJ83" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK83" s="3">
+      <c r="AK83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL83" s="3">
         <v>620500</v>
       </c>
-      <c r="AL83" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM83" s="3">
+      <c r="AM83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN83" s="3">
         <v>529600</v>
       </c>
-      <c r="AN83" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AO83" s="3">
+      <c r="AO83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP83" s="3">
         <v>413200</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>356800</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9035,8 +9237,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9157,8 +9362,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9279,8 +9487,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9401,8 +9612,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9523,35 +9737,38 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>429600</v>
+      </c>
+      <c r="E89" s="3">
         <v>216800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1633200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>383700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>454500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1019200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1514600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>214100</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>10</v>
       </c>
@@ -9567,86 +9784,89 @@
       <c r="P89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R89" s="3">
         <v>584800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-131800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-396100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-246300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4469700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>160500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>464500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>327700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1214800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>800200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>607600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>161500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1454600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>453200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>442300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>16700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2293600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-336700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>869600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>101000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1614500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-926800</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1676300</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>402600</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>2744400</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>-750100</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9689,35 +9909,36 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-73100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-84200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-97500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-79800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-74000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-59400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-85900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-83600</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>10</v>
       </c>
@@ -9733,86 +9954,89 @@
       <c r="P91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R91" s="3">
         <v>-247000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-196000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-182000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-181000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-217000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-208000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-81500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-79600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-133700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-128700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-130900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-120800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-213600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-142100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-136500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-123200</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AI91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-166900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-152600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-270400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-282700</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-200800</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-56300</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-1178500</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9933,8 +10157,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10055,35 +10282,38 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-21700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-468100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-230100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-185400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-264200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-169700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-102500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-151700</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>10</v>
       </c>
@@ -10099,8 +10329,8 @@
       <c r="P94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
@@ -10126,59 +10356,62 @@
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA94" s="3">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-572700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-23700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-237000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>82100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-587000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>38300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-626900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-368800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-684100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-95500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-3167400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-2451500</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-421900</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-122100</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-176100</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-525900</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10221,31 +10454,32 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
+      <c r="D96" s="3">
+        <v>366700</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>38700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>346400</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3" t="s">
-        <v>10</v>
+      <c r="I96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J96" s="3">
+        <v>0</v>
       </c>
       <c r="K96" s="3" t="s">
         <v>10</v>
@@ -10265,15 +10499,15 @@
       <c r="P96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-67000</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
@@ -10281,11 +10515,11 @@
         <v>0</v>
       </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-78600</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
@@ -10302,49 +10536,52 @@
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-4700</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-78400</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-10600</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-56500</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-374400</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-65100</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
       <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-365800</v>
       </c>
-      <c r="AN96" s="3">
-        <v>0</v>
-      </c>
       <c r="AO96" s="3">
         <v>0</v>
       </c>
       <c r="AP96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ96" s="3">
         <v>-58700</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10465,8 +10702,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10587,8 +10827,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10709,35 +10952,38 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1318400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-26500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-378100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-79800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>641200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-51900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-558000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-342400</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>10</v>
       </c>
@@ -10753,8 +10999,8 @@
       <c r="P100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
+      <c r="Q100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R100" s="3">
         <v>0</v>
@@ -10808,49 +11054,52 @@
         <v>0</v>
       </c>
       <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>-545700</v>
       </c>
-      <c r="AJ100" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK100" s="3">
+      <c r="AK100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL100" s="3">
         <v>622700</v>
       </c>
-      <c r="AL100" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM100" s="3">
+      <c r="AM100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN100" s="3">
         <v>-561000</v>
       </c>
-      <c r="AN100" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AO100" s="3">
+      <c r="AO100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP100" s="3">
         <v>-609200</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-192500</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-92800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-64900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>67300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-49100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>6400</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="I101" s="3" t="s">
         <v>10</v>
       </c>
@@ -10875,8 +11124,8 @@
       <c r="P101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10930,58 +11179,61 @@
         <v>0</v>
       </c>
       <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>5500</v>
       </c>
-      <c r="AJ101" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK101" s="3">
+      <c r="AK101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL101" s="3">
         <v>-71800</v>
       </c>
-      <c r="AL101" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM101" s="3">
+      <c r="AM101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN101" s="3">
         <v>-134600</v>
       </c>
-      <c r="AN101" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AO101" s="3">
+      <c r="AO101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP101" s="3">
         <v>35200</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-18800</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-917400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-232900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1036800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>105600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>738700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1305700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>921400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-329000</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
         <v>0</v>
       </c>
@@ -10991,14 +11243,14 @@
       <c r="N102" s="3">
         <v>0</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>10</v>
+      <c r="O102" s="3">
+        <v>0</v>
       </c>
       <c r="P102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
+      <c r="Q102" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R102" s="3">
         <v>0</v>
@@ -11052,27 +11304,30 @@
         <v>0</v>
       </c>
       <c r="AI102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>-354700</v>
       </c>
-      <c r="AJ102" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK102" s="3">
+      <c r="AK102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL102" s="3">
         <v>-1001900</v>
       </c>
-      <c r="AL102" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM102" s="3">
+      <c r="AM102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN102" s="3">
         <v>558800</v>
       </c>
-      <c r="AN102" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AO102" s="3">
+      <c r="AO102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP102" s="3">
         <v>558700</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-78600</v>
       </c>
     </row>
